--- a/docs/collections/nanki/metadata/data.xlsx
+++ b/docs/collections/nanki/metadata/data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="4401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="4715">
   <si>
     <t>書名</t>
   </si>
@@ -13218,6 +13218,948 @@
   </si>
   <si>
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c6bb30b8-7a85-9a0a-2af8-1384999734d7/manifest</t>
+  </si>
+  <si>
+    <t>蘐園雑話</t>
+  </si>
+  <si>
+    <t>A90:532</t>
+  </si>
+  <si>
+    <t>ケンエン ザツワ</t>
+  </si>
+  <si>
+    <t>不明</t>
+  </si>
+  <si>
+    <t>[書写地不明] : [書写者不明]</t>
+  </si>
+  <si>
+    <t>印記: 「坂田文庫」,「南葵文庫」|24cm</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f1708570-a084-682a-2b10-4b16d10f68c7.json</t>
+  </si>
+  <si>
+    <t>f1708570-a084-682a-2b10-4b16d10f68c7</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki/document/f1708570-a084-682a-2b10-4b16d10f68c7</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/41fcdc2b855f62ccc0795fc7d1a969a70f5636c8.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155821</t>
+  </si>
+  <si>
+    <t>0462</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f1708570-a084-682a-2b10-4b16d10f68c7/manifest</t>
+  </si>
+  <si>
+    <t>琉球往来 2巻</t>
+  </si>
+  <si>
+    <t>E26:1140</t>
+  </si>
+  <si>
+    <t>リュウキュウ オウライ</t>
+  </si>
+  <si>
+    <t>良定</t>
+  </si>
+  <si>
+    <t>天保7(1836)</t>
+  </si>
+  <si>
+    <t>題簽の書名: 琉球徃来|跋に「慶長八年癸卯當大明萬暦三十一年頃琉球国三年在留内依那覇港馬氏高明所請作之岱中□□(花押)」とあり|原奥書に「文化六己巳年十二月於京師得之藏 伴信友(花押)」とあり|奥書(朱書)に「天保七丙申年七月十三日課人令謄写加一?畢 長澤伴雄(花押)」とあり|印記: 「紀伊國徳川氏圖書記」,「陽春廬記」,「南葵文庫」|朱筆書き入れあり(巻末に「信友按岱中ハ岱中ナルヘシ琉球神道記ヲ作タル人ニテ琉球ヘ行タル人ナリ僧ナリナホ考ヘシ□□トアルハ字ナルカ」と朱書あり)|付箋あり 虫損あり|28cm</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/76c7dd01-61f6-68d2-9f3d-8aa34bca9565.json</t>
+  </si>
+  <si>
+    <t>76c7dd01-61f6-68d2-9f3d-8aa34bca9565</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki/document/76c7dd01-61f6-68d2-9f3d-8aa34bca9565</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e8727451f48b752595baa06af70507e5675c0cef.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155820</t>
+  </si>
+  <si>
+    <t>0463</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/76c7dd01-61f6-68d2-9f3d-8aa34bca9565/manifest</t>
+  </si>
+  <si>
+    <t>亞墨竹枝</t>
+  </si>
+  <si>
+    <t>E43:913</t>
+  </si>
+  <si>
+    <t>アボク チクシ</t>
+  </si>
+  <si>
+    <t>井上黙撰</t>
+  </si>
+  <si>
+    <t>[出版地不明] : [學半堂]</t>
+  </si>
+  <si>
+    <t>[弘化3(1846)] 跋</t>
+  </si>
+  <si>
+    <t>見返しに「學半堂藏」とあり|序末に「丙午仲秋廣瀬建書」, 「丙午春二月 浪蕐小竹散人筱崎弻」, 「弘化乙巳仲秋秋香山人前川文撰」とあり|跋末に「弘化乙巳仲秋秋田晴吉書」, 「丙午春仲 檉園主人小石龍識」とあり|左右双辺有界9行20字, 内匡廓: 17.1×11.7cm, 上黒魚尾白口|印記: 「陽春廬記」, 「紀伊徳川 南葵文庫」|23cm|亜墨竹枝</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7a2c46c2-8605-4a92-48b5-7b4810c61e22.json</t>
+  </si>
+  <si>
+    <t>7a2c46c2-8605-4a92-48b5-7b4810c61e22</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki/document/7a2c46c2-8605-4a92-48b5-7b4810c61e22</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/304c78888e6966d129c4e16e5f32a95a3a576f92.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155819</t>
+  </si>
+  <si>
+    <t>0464</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7a2c46c2-8605-4a92-48b5-7b4810c61e22/manifest</t>
+  </si>
+  <si>
+    <t>二十四孝和歌</t>
+  </si>
+  <si>
+    <t>E31:899</t>
+  </si>
+  <si>
+    <t>ニジュウシコウカ</t>
+  </si>
+  <si>
+    <t>常操 [ほか詠]</t>
+  </si>
+  <si>
+    <t>[幕末明治期]</t>
+  </si>
+  <si>
+    <t>扉の書名: 廿四孝歌|題簽の書名: 二十四孝和謌|四周双辺有界10行単魚尾の罫紙を使用|印記: 「坂田文庫」, 「南葵文庫」|24cm|廿四孝歌, 二十四孝和謌</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/2ee61918-9943-4865-1ccd-4889216976ec.json</t>
+  </si>
+  <si>
+    <t>2ee61918-9943-4865-1ccd-4889216976ec</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki/document/2ee61918-9943-4865-1ccd-4889216976ec</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7318da2a06ab345305af3452b08af43bb7bffe76.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155818</t>
+  </si>
+  <si>
+    <t>0465</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/2ee61918-9943-4865-1ccd-4889216976ec/manifest</t>
+  </si>
+  <si>
+    <t>黄葉和歌集 5巻第1</t>
+  </si>
+  <si>
+    <t>E31:1351</t>
+  </si>
+  <si>
+    <t>コウヨウ ワカシュウ</t>
+  </si>
+  <si>
+    <t>光廣 [詠] ; 資慶 [編]</t>
+  </si>
+  <si>
+    <t>亰師 : 中井平治郎 : 吉田四郎右衞門</t>
+  </si>
+  <si>
+    <t>寛保3(1743)</t>
+  </si>
+  <si>
+    <t>[跋]中の書名: 黄葉和歌|[跋]末に「寛文九年仲夏上浣/嫡孫持進資慶」とあり|刊記に「寛保三癸亥年正月吉日/亰師書林 二条通冨小路東江入町 吉田四郎右衞門/寺町通竹屋町下町 中井平治郎 」とあり|四周無辺無界13行|後印本|印記: 「小倉文庫」, 「原宿文庫」, 「交埜藏書」, 「南葵文庫」|23cm|黄葉和歌,烏丸光広家集</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d38eb709-68b8-8f16-5793-5ba0fe8f0801.json</t>
+  </si>
+  <si>
+    <t>d38eb709-68b8-8f16-5793-5ba0fe8f0801</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki/document/d38eb709-68b8-8f16-5793-5ba0fe8f0801</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/144f72fff442ba6c37db692c49de63f9993e6f28.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155817</t>
+  </si>
+  <si>
+    <t>0466</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d38eb709-68b8-8f16-5793-5ba0fe8f0801/manifest</t>
+  </si>
+  <si>
+    <t>黄葉和歌集 5巻第2</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7461aa9d-6fd7-3e05-2d98-cbab89ee03c7.json</t>
+  </si>
+  <si>
+    <t>7461aa9d-6fd7-3e05-2d98-cbab89ee03c7</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki/document/7461aa9d-6fd7-3e05-2d98-cbab89ee03c7</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8690780a61998abbb0f2c4f8b9fc212b19b2ae53.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155816</t>
+  </si>
+  <si>
+    <t>0467</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7461aa9d-6fd7-3e05-2d98-cbab89ee03c7/manifest</t>
+  </si>
+  <si>
+    <t>黄葉和歌集 5巻第3</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/72080b90-58bc-3050-5b2f-8f05c555065a.json</t>
+  </si>
+  <si>
+    <t>72080b90-58bc-3050-5b2f-8f05c555065a</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki/document/72080b90-58bc-3050-5b2f-8f05c555065a</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/01af456a364ad1857a3cdf6143c6d58be8d4c5a4.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155815</t>
+  </si>
+  <si>
+    <t>0468</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/72080b90-58bc-3050-5b2f-8f05c555065a/manifest</t>
+  </si>
+  <si>
+    <t>黄葉和歌集 5巻第4</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/385271a7-7469-4d41-0734-223b56719ac4.json</t>
+  </si>
+  <si>
+    <t>385271a7-7469-4d41-0734-223b56719ac4</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki/document/385271a7-7469-4d41-0734-223b56719ac4</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/366ccdf8f3fdc11e00e41cfaad8548dcee91c945.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155814</t>
+  </si>
+  <si>
+    <t>0469</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/385271a7-7469-4d41-0734-223b56719ac4/manifest</t>
+  </si>
+  <si>
+    <t>黄葉和歌集 5巻第5</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d92158ea-719b-4a4c-9645-91d5909982fb.json</t>
+  </si>
+  <si>
+    <t>d92158ea-719b-4a4c-9645-91d5909982fb</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki/document/d92158ea-719b-4a4c-9645-91d5909982fb</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0a7933c13a74ddf1278b4deee725e7b80a1cb724.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155813</t>
+  </si>
+  <si>
+    <t>0470</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d92158ea-719b-4a4c-9645-91d5909982fb/manifest</t>
+  </si>
+  <si>
+    <t>江戸町鑒</t>
+  </si>
+  <si>
+    <t>SJ:66</t>
+  </si>
+  <si>
+    <t>エド チョウカン</t>
+  </si>
+  <si>
+    <t>松栢堂主人 [校訂]</t>
+  </si>
+  <si>
+    <t>江戸 : 出雲寺金吾</t>
+  </si>
+  <si>
+    <t>天保13(1842)</t>
+  </si>
+  <si>
+    <t>書名は見返しによる|又丁あり|印記: 「南葵文庫」|8×19cm|江戸町鑑</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9e05ccf0-1518-3fe3-9255-ff1cdbe76231.json</t>
+  </si>
+  <si>
+    <t>9e05ccf0-1518-3fe3-9255-ff1cdbe76231</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki/document/9e05ccf0-1518-3fe3-9255-ff1cdbe76231</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/04ecff253addcfb996cfa4c321181bfb02d0cb20.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155812</t>
+  </si>
+  <si>
+    <t>0471</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9e05ccf0-1518-3fe3-9255-ff1cdbe76231/manifest</t>
+  </si>
+  <si>
+    <t>増補改正萬世江戸町鑑  2巻上</t>
+  </si>
+  <si>
+    <t>J40:473</t>
+  </si>
+  <si>
+    <t>ゾウホ カイセイ バンセイ エド マチカガミ</t>
+  </si>
+  <si>
+    <t>江戸 : 須原屋伊八 : 須原屋佐助 : 須原屋茂兵衞</t>
+  </si>
+  <si>
+    <t>萬延元(1860)</t>
+  </si>
+  <si>
+    <t>書名は目首による|目尾及び題簽の書名: 萬世江戸町鑑|見返しの書名: 萬世江戸町鑑 : 改正増補|版心の書名: 町|巻次は題簽及び版心による|見返しに「萬延元庚申年改」とあり|又丁あり|印記: 「富田」,「坂田文庫」,「南葵文庫」|16cm|江戸町鑑 : 萬世 : 改正増補</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4f3d82c9-721c-668f-29d3-20a947eb0783.json</t>
+  </si>
+  <si>
+    <t>4f3d82c9-721c-668f-29d3-20a947eb0783</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki/document/4f3d82c9-721c-668f-29d3-20a947eb0783</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/247c2ff91cca938a382c384ad99e9ed17bdb9a45.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155811</t>
+  </si>
+  <si>
+    <t>0472</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4f3d82c9-721c-668f-29d3-20a947eb0783/manifest</t>
+  </si>
+  <si>
+    <t>増補改正萬世江戸町鑑  2巻下</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9b16e59a-7060-6eee-1e8f-8b461b8e9c46.json</t>
+  </si>
+  <si>
+    <t>9b16e59a-7060-6eee-1e8f-8b461b8e9c46</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki/document/9b16e59a-7060-6eee-1e8f-8b461b8e9c46</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/89effd4c5987da43874ab9abdda4e8ec10d0e74b.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155810</t>
+  </si>
+  <si>
+    <t>0473</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9b16e59a-7060-6eee-1e8f-8b461b8e9c46/manifest</t>
+  </si>
+  <si>
+    <t>J40:474</t>
+  </si>
+  <si>
+    <t>嘉永5(1852)</t>
+  </si>
+  <si>
+    <t>書名は目首による|目尾及び題簽の書名: 萬世江戸町鑑|見返しの書名: 萬世江戸町鑑 : 改正増補|版心の書名: 町|巻次は題簽及び版心による|見返しに「嘉永五子年改」とあり|又丁あり|印記: 「坂田文庫」,「南葵文庫」|16cm|江戸町鑑 : 萬世 : 改正増補</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8c7df6b2-1cac-7304-a3eb-ce5e28be3d22.json</t>
+  </si>
+  <si>
+    <t>8c7df6b2-1cac-7304-a3eb-ce5e28be3d22</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki/document/8c7df6b2-1cac-7304-a3eb-ce5e28be3d22</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c1c89e9b00946d6267f73c8f40b735f188c93cdb.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155809</t>
+  </si>
+  <si>
+    <t>0474</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8c7df6b2-1cac-7304-a3eb-ce5e28be3d22/manifest</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e7ce1ac9-2876-4ab0-2d08-406d9f1007cf.json</t>
+  </si>
+  <si>
+    <t>e7ce1ac9-2876-4ab0-2d08-406d9f1007cf</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki/document/e7ce1ac9-2876-4ab0-2d08-406d9f1007cf</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b8dfd51f15b4dc9e3ae1c663194d9af31c6dd5bc.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155808</t>
+  </si>
+  <si>
+    <t>0475</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e7ce1ac9-2876-4ab0-2d08-406d9f1007cf/manifest</t>
+  </si>
+  <si>
+    <t>J40:475</t>
+  </si>
+  <si>
+    <t>安政4(1857)</t>
+  </si>
+  <si>
+    <t>書名は目首による|目尾及び題簽の書名: 萬世江戸町鑑|見返しの書名: 萬世江戸町鑑 : 改正増補|版心の書名: 町|巻次は題簽及び版心による|見返しに「安政四巳年改」とあり|又丁あり|印記: 「南葵文庫」|16cm|江戸町鑑 : 萬世 : 改正増補</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e9f371fc-92a4-3aae-744d-48cf0e9c436f.json</t>
+  </si>
+  <si>
+    <t>e9f371fc-92a4-3aae-744d-48cf0e9c436f</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki/document/e9f371fc-92a4-3aae-744d-48cf0e9c436f</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/9d72536d95ffaea5db13b50bf43c9aa8b383da0d.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155807</t>
+  </si>
+  <si>
+    <t>0476</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e9f371fc-92a4-3aae-744d-48cf0e9c436f/manifest</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/93967f9c-39a7-9f4c-99dc-1e4e2d8f7ab8.json</t>
+  </si>
+  <si>
+    <t>93967f9c-39a7-9f4c-99dc-1e4e2d8f7ab8</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki/document/93967f9c-39a7-9f4c-99dc-1e4e2d8f7ab8</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/5f1f99bae1cbe30e4ae76cad3bd90363921f496f.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155806</t>
+  </si>
+  <si>
+    <t>0477</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/93967f9c-39a7-9f4c-99dc-1e4e2d8f7ab8/manifest</t>
+  </si>
+  <si>
+    <t>隠州視聴合記 4巻</t>
+  </si>
+  <si>
+    <t>J30:655</t>
+  </si>
+  <si>
+    <t>インシュウ シチョウ ゴウキ</t>
+  </si>
+  <si>
+    <t>藤弗緩 [著]</t>
+  </si>
+  <si>
+    <t>序末に「寛文七年冬十月藤弗緩釆毫矢尾舘下」とあり|印記: 「中川家藏書印」,「中川」,「南葵文庫」|27cm</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/719e193d-6044-3b9e-904f-4474d62ca6d4.json</t>
+  </si>
+  <si>
+    <t>719e193d-6044-3b9e-904f-4474d62ca6d4</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki/document/719e193d-6044-3b9e-904f-4474d62ca6d4</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/312ea2d98c98122ed9769cc9b7499cea8a3acecf.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155805</t>
+  </si>
+  <si>
+    <t>0478</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/719e193d-6044-3b9e-904f-4474d62ca6d4/manifest</t>
+  </si>
+  <si>
+    <t>隠州視聴合記 4巻1-2</t>
+  </si>
+  <si>
+    <t>J30:927</t>
+  </si>
+  <si>
+    <t>[斎藤弗緩著]</t>
+  </si>
+  <si>
+    <t>題簽の書名: 隱州視聴合記|責任表示は『日本古典籍総合目録データベース』による|印記: 「紀伊國徳川氏圖書記」,「南葵文庫」|27cm|隱州視聴合記</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c5578325-889e-43e3-9efb-5044360d4c92.json</t>
+  </si>
+  <si>
+    <t>c5578325-889e-43e3-9efb-5044360d4c92</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki/document/c5578325-889e-43e3-9efb-5044360d4c92</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b501298e58474ef42c08be6a72f9b32d341bdfd1.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155804</t>
+  </si>
+  <si>
+    <t>0479</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c5578325-889e-43e3-9efb-5044360d4c92/manifest</t>
+  </si>
+  <si>
+    <t>隠州視聴合記 4巻3-4</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/3c8e5518-8bbe-489f-3dc9-d5507160342d.json</t>
+  </si>
+  <si>
+    <t>3c8e5518-8bbe-489f-3dc9-d5507160342d</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki/document/3c8e5518-8bbe-489f-3dc9-d5507160342d</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/ab35f90e637c8f160421e4f4c649dea3c2d930e1.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155803</t>
+  </si>
+  <si>
+    <t>0480</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3c8e5518-8bbe-489f-3dc9-d5507160342d/manifest</t>
+  </si>
+  <si>
+    <t>大かゝみ1</t>
+  </si>
+  <si>
+    <t>G24:349</t>
+  </si>
+  <si>
+    <t>書名は題簽と小口による|冊次は題簽による|内容: 1:第五十五代...左大臣師尹. 2: 右大臣師輔...左大臣道兼. 3: 太政大臣道長|印記: 「八雲軒」, 「安元」, 「藤亨」(脇坂安元), 「陽春廬記」(小中村清矩), 「紀伊恴川 南葵文庫」|虫損あり|27.9×19.1cm|大鏡</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/cdc4cc06-46aa-5349-1b1e-56478e899452.json</t>
+  </si>
+  <si>
+    <t>cdc4cc06-46aa-5349-1b1e-56478e899452</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki/document/cdc4cc06-46aa-5349-1b1e-56478e899452</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1ab829adcbd613a488a99913e0f13bea61e4ab1d.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155802</t>
+  </si>
+  <si>
+    <t>0481</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/cdc4cc06-46aa-5349-1b1e-56478e899452/manifest</t>
+  </si>
+  <si>
+    <t>大かゝみ2</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ba46794d-9cda-33f7-8e83-c43c0fca4e61.json</t>
+  </si>
+  <si>
+    <t>ba46794d-9cda-33f7-8e83-c43c0fca4e61</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki/document/ba46794d-9cda-33f7-8e83-c43c0fca4e61</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0f995b5a5c4228b058fb08eae94d65f157c2f191.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155801</t>
+  </si>
+  <si>
+    <t>0482</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ba46794d-9cda-33f7-8e83-c43c0fca4e61/manifest</t>
+  </si>
+  <si>
+    <t>大かゝみ3</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e7243dad-a70f-215e-8479-dc95762424ea.json</t>
+  </si>
+  <si>
+    <t>e7243dad-a70f-215e-8479-dc95762424ea</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki/document/e7243dad-a70f-215e-8479-dc95762424ea</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8d0aa78a329d0b8018eb3383a1eeb91d540fd081.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155800</t>
+  </si>
+  <si>
+    <t>0483</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e7243dad-a70f-215e-8479-dc95762424ea/manifest</t>
+  </si>
+  <si>
+    <t>御室和書目録</t>
+  </si>
+  <si>
+    <t>A00:6190</t>
+  </si>
+  <si>
+    <t>オムロ ワショ モクロク</t>
+  </si>
+  <si>
+    <t>藤實冬 [傳]</t>
+  </si>
+  <si>
+    <t>[書写地不明] : 山縣昌貞 [写]</t>
+  </si>
+  <si>
+    <t>寳暦13(1763) 奥書</t>
+  </si>
+  <si>
+    <t>表紙に「一曰仁和寺書目」とあり|跋末に「右書大納言藤實冬卿私借得讀之聊加禿筆以為證如此 永正二年八月四日大外記中原師名跋」とあり|奥書に「御室和書目録一冊維章所校余更繕冩其有謬誤者從而正之 ... 寳暦十三年癸未十一月中旬山縣昌貞手書」とあり|毎半葉10行注文双行|頭注あり|印記: 「海保先生遺書」, 「島田氏雙桂樓収臧」(島田篁村), 「南葵文庫」|虫損あり|28×18cm|仁和寺書目,本朝書籍目録</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/02721a63-2958-39d7-1115-35577dec86fa.json</t>
+  </si>
+  <si>
+    <t>02721a63-2958-39d7-1115-35577dec86fa</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki/document/02721a63-2958-39d7-1115-35577dec86fa</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/996fa27c23c98e684408ec8476e99144ca12ccde.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155799</t>
+  </si>
+  <si>
+    <t>0484</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/02721a63-2958-39d7-1115-35577dec86fa/manifest</t>
+  </si>
+  <si>
+    <t>嶋原日記 8巻3</t>
+  </si>
+  <si>
+    <t>G24:705</t>
+  </si>
+  <si>
+    <t>シマバラ ニッキ</t>
+  </si>
+  <si>
+    <t>書名と巻次は題簽による|1-2,10の題簽の書名: 島原日記|小口の書名: 島日|遊び紙に「丑/細川越中殿家老并嶋原隣國より集候書状之多」とあり|墨筆書入れあり|印記: 「紀伊國徳川氏圖書記」,「紀伊恴川 南葵文庫」|虫損あり|27.5×21.0cm|島原日記,島日</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0eb3ec9b-0cd9-81c6-8fdf-21f3fdd38f44.json</t>
+  </si>
+  <si>
+    <t>0eb3ec9b-0cd9-81c6-8fdf-21f3fdd38f44</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki/document/0eb3ec9b-0cd9-81c6-8fdf-21f3fdd38f44</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3e56cd8a49739fa191362633364f4dca8f6a2fbd.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155798</t>
+  </si>
+  <si>
+    <t>0485</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0eb3ec9b-0cd9-81c6-8fdf-21f3fdd38f44/manifest</t>
+  </si>
+  <si>
+    <t>嶋原日記 8巻4</t>
+  </si>
+  <si>
+    <t>書名と巻次は題簽による|1-2,11の題簽の書名: 島原日記|小口の書名: 島日|遊び紙に「丑/細川越中殿家老并嶋原隣國より集候書状之多」とあり|墨筆書入れあり|印記: 「紀伊國徳川氏圖書記」,「紀伊恴川 南葵文庫」|虫損あり|27.5×21.0cm|島原日記,島日</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7cf4f5a6-781c-9b06-2fb5-9a6c75585c2e.json</t>
+  </si>
+  <si>
+    <t>7cf4f5a6-781c-9b06-2fb5-9a6c75585c2e</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki/document/7cf4f5a6-781c-9b06-2fb5-9a6c75585c2e</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/471257fcd0da1913424a89fdea733772c6cf6803.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155797</t>
+  </si>
+  <si>
+    <t>0486</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7cf4f5a6-781c-9b06-2fb5-9a6c75585c2e/manifest</t>
+  </si>
+  <si>
+    <t>嶋原日記 8巻5</t>
+  </si>
+  <si>
+    <t>書名と巻次は題簽による|1-2,12の題簽の書名: 島原日記|小口の書名: 島日|遊び紙に「丑/細川越中殿家老并嶋原隣國より集候書状之多」とあり|墨筆書入れあり|印記: 「紀伊國徳川氏圖書記」,「紀伊恴川 南葵文庫」|虫損あり|27.5×21.0cm|島原日記,島日</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4b417f30-38f1-501b-9b3a-a83ea6bf0c4b.json</t>
+  </si>
+  <si>
+    <t>4b417f30-38f1-501b-9b3a-a83ea6bf0c4b</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki/document/4b417f30-38f1-501b-9b3a-a83ea6bf0c4b</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/5307ddd18db0c7b0041131c5b43f5ff0749cd994.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155796</t>
+  </si>
+  <si>
+    <t>0487</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4b417f30-38f1-501b-9b3a-a83ea6bf0c4b/manifest</t>
+  </si>
+  <si>
+    <t>嶋原日記 8巻6</t>
+  </si>
+  <si>
+    <t>書名と巻次は題簽による|1-2,13の題簽の書名: 島原日記|小口の書名: 島日|遊び紙に「丑/細川越中殿家老并嶋原隣國より集候書状之多」とあり|墨筆書入れあり|印記: 「紀伊國徳川氏圖書記」,「紀伊恴川 南葵文庫」|虫損あり|27.5×21.0cm|島原日記,島日</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b6a0d16e-07d5-16ef-8064-966b40fe6431.json</t>
+  </si>
+  <si>
+    <t>b6a0d16e-07d5-16ef-8064-966b40fe6431</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki/document/b6a0d16e-07d5-16ef-8064-966b40fe6431</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/075bdf9e2c29b124e41af770ed114d5c5c6922ef.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155795</t>
+  </si>
+  <si>
+    <t>0488</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b6a0d16e-07d5-16ef-8064-966b40fe6431/manifest</t>
+  </si>
+  <si>
+    <t>嶋原日記 8巻7</t>
+  </si>
+  <si>
+    <t>書名と巻次は題簽による|1-2,14の題簽の書名: 島原日記|小口の書名: 島日|遊び紙に「丑/細川越中殿家老并嶋原隣國より集候書状之多」とあり|墨筆書入れあり|印記: 「紀伊國徳川氏圖書記」,「紀伊恴川 南葵文庫」|虫損あり|27.5×21.0cm|島原日記,島日</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0532a51d-3194-8daf-46b6-5613d3a01355.json</t>
+  </si>
+  <si>
+    <t>0532a51d-3194-8daf-46b6-5613d3a01355</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki/document/0532a51d-3194-8daf-46b6-5613d3a01355</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/88b1bf41ad479a3852dd55d8afafcbf90d65e098.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155794</t>
+  </si>
+  <si>
+    <t>0489</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0532a51d-3194-8daf-46b6-5613d3a01355/manifest</t>
+  </si>
+  <si>
+    <t>嶋原日記 8巻8</t>
+  </si>
+  <si>
+    <t>書名と巻次は題簽による|1-2,15の題簽の書名: 島原日記|小口の書名: 島日|遊び紙に「丑/細川越中殿家老并嶋原隣國より集候書状之多」とあり|墨筆書入れあり|印記: 「紀伊國徳川氏圖書記」,「紀伊恴川 南葵文庫」|虫損あり|27.5×21.0cm|島原日記,島日</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0e0e0e9f-7a58-12c2-4014-f08d6c985c4a.json</t>
+  </si>
+  <si>
+    <t>0e0e0e9f-7a58-12c2-4014-f08d6c985c4a</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki/document/0e0e0e9f-7a58-12c2-4014-f08d6c985c4a</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/749bddfd6263c853d585e7ca4b284cddfd9477c3.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155793</t>
+  </si>
+  <si>
+    <t>0490</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0e0e0e9f-7a58-12c2-4014-f08d6c985c4a/manifest</t>
+  </si>
+  <si>
+    <t>嶋原日記 8巻 1</t>
+  </si>
+  <si>
+    <t>書名と巻次は題簽による|1-2,8の題簽の書名: 島原日記|小口の書名: 島日|遊び紙に「丑/細川越中殿家老并嶋原隣國より集候書状之多」とあり|墨筆書入れあり|印記: 「紀伊國徳川氏圖書記」,「紀伊恴川 南葵文庫」|虫損あり|27.5×21.0cm|島原日記,島日</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7b429652-3441-0070-3b6c-0116f7053835.json</t>
+  </si>
+  <si>
+    <t>7b429652-3441-0070-3b6c-0116f7053835</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki/document/7b429652-3441-0070-3b6c-0116f7053835</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a9baf71d7f0142eab0840d9731ae601f6a281f22.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155792</t>
+  </si>
+  <si>
+    <t>0491</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7b429652-3441-0070-3b6c-0116f7053835/manifest</t>
+  </si>
+  <si>
+    <t>嶋原日記 8巻2</t>
+  </si>
+  <si>
+    <t>書名と巻次は題簽による|1-2,9の題簽の書名: 島原日記|小口の書名: 島日|遊び紙に「丑/細川越中殿家老并嶋原隣國より集候書状之多」とあり|墨筆書入れあり|印記: 「紀伊國徳川氏圖書記」,「紀伊恴川 南葵文庫」|虫損あり|27.5×21.0cm|島原日記,島日</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c33074a5-553b-65d5-3a35-33e3e85913d4.json</t>
+  </si>
+  <si>
+    <t>c33074a5-553b-65d5-3a35-33e3e85913d4</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/nanki/document/c33074a5-553b-65d5-3a35-33e3e85913d4</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c06f9129f5d0dfd0303a82339f6db71fc1d8feaf.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155791</t>
+  </si>
+  <si>
+    <t>0492</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c33074a5-553b-65d5-3a35-33e3e85913d4/manifest</t>
   </si>
 </sst>
 </file>
@@ -13553,7 +14495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC464"/>
+  <dimension ref="A1:AC495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:29">
@@ -13731,7 +14673,7 @@
         <v>55</v>
       </c>
       <c r="AC2" t="n">
-        <v>30038</v>
+        <v>31979</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -49098,6 +50040,2393 @@
         <v>19</v>
       </c>
     </row>
+    <row r="465" spans="1:29">
+      <c r="A465" t="s">
+        <v>4401</v>
+      </c>
+      <c r="B465" t="s">
+        <v>4402</v>
+      </c>
+      <c r="C465" t="s">
+        <v>4403</v>
+      </c>
+      <c r="D465" t="s">
+        <v>4404</v>
+      </c>
+      <c r="E465" t="s">
+        <v>192</v>
+      </c>
+      <c r="F465" t="s">
+        <v>4405</v>
+      </c>
+      <c r="G465" t="s">
+        <v>4314</v>
+      </c>
+      <c r="H465" t="s">
+        <v>195</v>
+      </c>
+      <c r="I465" t="s">
+        <v>196</v>
+      </c>
+      <c r="J465" t="s">
+        <v>4406</v>
+      </c>
+      <c r="K465" t="s">
+        <v>4407</v>
+      </c>
+      <c r="L465" t="s">
+        <v>4408</v>
+      </c>
+      <c r="M465" t="s">
+        <v>4409</v>
+      </c>
+      <c r="N465" t="s">
+        <v>4410</v>
+      </c>
+      <c r="O465" t="s">
+        <v>70</v>
+      </c>
+      <c r="P465" t="s">
+        <v>4411</v>
+      </c>
+      <c r="Q465" t="s">
+        <v>4412</v>
+      </c>
+      <c r="R465" t="s">
+        <v>73</v>
+      </c>
+      <c r="S465" t="s">
+        <v>74</v>
+      </c>
+      <c r="T465" t="s"/>
+      <c r="U465" t="s">
+        <v>75</v>
+      </c>
+      <c r="V465" t="s">
+        <v>4413</v>
+      </c>
+      <c r="W465" t="s"/>
+      <c r="X465" t="s">
+        <v>4414</v>
+      </c>
+      <c r="Y465" t="s"/>
+      <c r="Z465" t="s"/>
+      <c r="AA465" t="s"/>
+      <c r="AB465" t="s"/>
+      <c r="AC465" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="466" spans="1:29">
+      <c r="A466" t="s">
+        <v>4415</v>
+      </c>
+      <c r="B466" t="s">
+        <v>4416</v>
+      </c>
+      <c r="C466" t="s">
+        <v>4417</v>
+      </c>
+      <c r="D466" t="s">
+        <v>4418</v>
+      </c>
+      <c r="E466" t="s">
+        <v>192</v>
+      </c>
+      <c r="F466" t="s">
+        <v>370</v>
+      </c>
+      <c r="G466" t="s">
+        <v>4419</v>
+      </c>
+      <c r="H466" t="s">
+        <v>195</v>
+      </c>
+      <c r="I466" t="s">
+        <v>196</v>
+      </c>
+      <c r="J466" t="s">
+        <v>4420</v>
+      </c>
+      <c r="K466" t="s">
+        <v>4421</v>
+      </c>
+      <c r="L466" t="s">
+        <v>4422</v>
+      </c>
+      <c r="M466" t="s">
+        <v>4409</v>
+      </c>
+      <c r="N466" t="s">
+        <v>4423</v>
+      </c>
+      <c r="O466" t="s">
+        <v>70</v>
+      </c>
+      <c r="P466" t="s">
+        <v>4424</v>
+      </c>
+      <c r="Q466" t="s">
+        <v>4425</v>
+      </c>
+      <c r="R466" t="s">
+        <v>73</v>
+      </c>
+      <c r="S466" t="s">
+        <v>74</v>
+      </c>
+      <c r="T466" t="s"/>
+      <c r="U466" t="s">
+        <v>75</v>
+      </c>
+      <c r="V466" t="s">
+        <v>4426</v>
+      </c>
+      <c r="W466" t="s"/>
+      <c r="X466" t="s">
+        <v>4427</v>
+      </c>
+      <c r="Y466" t="s"/>
+      <c r="Z466" t="s"/>
+      <c r="AA466" t="s"/>
+      <c r="AB466" t="s"/>
+      <c r="AC466" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="467" spans="1:29">
+      <c r="A467" t="s">
+        <v>4428</v>
+      </c>
+      <c r="B467" t="s">
+        <v>4429</v>
+      </c>
+      <c r="C467" t="s">
+        <v>4430</v>
+      </c>
+      <c r="D467" t="s">
+        <v>4431</v>
+      </c>
+      <c r="E467" t="s">
+        <v>192</v>
+      </c>
+      <c r="F467" t="s">
+        <v>4432</v>
+      </c>
+      <c r="G467" t="s">
+        <v>4433</v>
+      </c>
+      <c r="H467" t="s">
+        <v>195</v>
+      </c>
+      <c r="I467" t="s">
+        <v>196</v>
+      </c>
+      <c r="J467" t="s">
+        <v>4434</v>
+      </c>
+      <c r="K467" t="s">
+        <v>4435</v>
+      </c>
+      <c r="L467" t="s">
+        <v>4436</v>
+      </c>
+      <c r="M467" t="s">
+        <v>4409</v>
+      </c>
+      <c r="N467" t="s">
+        <v>4437</v>
+      </c>
+      <c r="O467" t="s">
+        <v>70</v>
+      </c>
+      <c r="P467" t="s">
+        <v>4438</v>
+      </c>
+      <c r="Q467" t="s">
+        <v>4439</v>
+      </c>
+      <c r="R467" t="s">
+        <v>73</v>
+      </c>
+      <c r="S467" t="s">
+        <v>74</v>
+      </c>
+      <c r="T467" t="s"/>
+      <c r="U467" t="s">
+        <v>75</v>
+      </c>
+      <c r="V467" t="s">
+        <v>4440</v>
+      </c>
+      <c r="W467" t="s"/>
+      <c r="X467" t="s">
+        <v>4441</v>
+      </c>
+      <c r="Y467" t="s"/>
+      <c r="Z467" t="s"/>
+      <c r="AA467" t="s"/>
+      <c r="AB467" t="s"/>
+      <c r="AC467" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="468" spans="1:29">
+      <c r="A468" t="s">
+        <v>4442</v>
+      </c>
+      <c r="B468" t="s">
+        <v>4443</v>
+      </c>
+      <c r="C468" t="s">
+        <v>4444</v>
+      </c>
+      <c r="D468" t="s">
+        <v>4445</v>
+      </c>
+      <c r="E468" t="s">
+        <v>192</v>
+      </c>
+      <c r="F468" t="s">
+        <v>4405</v>
+      </c>
+      <c r="G468" t="s">
+        <v>4446</v>
+      </c>
+      <c r="H468" t="s">
+        <v>195</v>
+      </c>
+      <c r="I468" t="s">
+        <v>196</v>
+      </c>
+      <c r="J468" t="s">
+        <v>4447</v>
+      </c>
+      <c r="K468" t="s">
+        <v>4448</v>
+      </c>
+      <c r="L468" t="s">
+        <v>4449</v>
+      </c>
+      <c r="M468" t="s">
+        <v>4409</v>
+      </c>
+      <c r="N468" t="s">
+        <v>4450</v>
+      </c>
+      <c r="O468" t="s">
+        <v>70</v>
+      </c>
+      <c r="P468" t="s">
+        <v>4451</v>
+      </c>
+      <c r="Q468" t="s">
+        <v>4452</v>
+      </c>
+      <c r="R468" t="s">
+        <v>73</v>
+      </c>
+      <c r="S468" t="s">
+        <v>74</v>
+      </c>
+      <c r="T468" t="s"/>
+      <c r="U468" t="s">
+        <v>75</v>
+      </c>
+      <c r="V468" t="s">
+        <v>4453</v>
+      </c>
+      <c r="W468" t="s"/>
+      <c r="X468" t="s">
+        <v>4454</v>
+      </c>
+      <c r="Y468" t="s"/>
+      <c r="Z468" t="s"/>
+      <c r="AA468" t="s"/>
+      <c r="AB468" t="s"/>
+      <c r="AC468" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="469" spans="1:29">
+      <c r="A469" t="s">
+        <v>4455</v>
+      </c>
+      <c r="B469" t="s">
+        <v>4456</v>
+      </c>
+      <c r="C469" t="s">
+        <v>4457</v>
+      </c>
+      <c r="D469" t="s">
+        <v>4458</v>
+      </c>
+      <c r="E469" t="s">
+        <v>60</v>
+      </c>
+      <c r="F469" t="s">
+        <v>4459</v>
+      </c>
+      <c r="G469" t="s">
+        <v>4460</v>
+      </c>
+      <c r="H469" t="s">
+        <v>195</v>
+      </c>
+      <c r="I469" t="s">
+        <v>196</v>
+      </c>
+      <c r="J469" t="s">
+        <v>4461</v>
+      </c>
+      <c r="K469" t="s">
+        <v>4462</v>
+      </c>
+      <c r="L469" t="s">
+        <v>4463</v>
+      </c>
+      <c r="M469" t="s">
+        <v>4409</v>
+      </c>
+      <c r="N469" t="s">
+        <v>4464</v>
+      </c>
+      <c r="O469" t="s">
+        <v>70</v>
+      </c>
+      <c r="P469" t="s">
+        <v>4465</v>
+      </c>
+      <c r="Q469" t="s">
+        <v>4466</v>
+      </c>
+      <c r="R469" t="s">
+        <v>73</v>
+      </c>
+      <c r="S469" t="s">
+        <v>74</v>
+      </c>
+      <c r="T469" t="s"/>
+      <c r="U469" t="s">
+        <v>75</v>
+      </c>
+      <c r="V469" t="s">
+        <v>4467</v>
+      </c>
+      <c r="W469" t="s"/>
+      <c r="X469" t="s">
+        <v>4468</v>
+      </c>
+      <c r="Y469" t="s"/>
+      <c r="Z469" t="s"/>
+      <c r="AA469" t="s"/>
+      <c r="AB469" t="s"/>
+      <c r="AC469" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="470" spans="1:29">
+      <c r="A470" t="s">
+        <v>4469</v>
+      </c>
+      <c r="B470" t="s">
+        <v>4456</v>
+      </c>
+      <c r="C470" t="s">
+        <v>4457</v>
+      </c>
+      <c r="D470" t="s">
+        <v>4458</v>
+      </c>
+      <c r="E470" t="s">
+        <v>60</v>
+      </c>
+      <c r="F470" t="s">
+        <v>4459</v>
+      </c>
+      <c r="G470" t="s">
+        <v>4460</v>
+      </c>
+      <c r="H470" t="s">
+        <v>195</v>
+      </c>
+      <c r="I470" t="s">
+        <v>196</v>
+      </c>
+      <c r="J470" t="s">
+        <v>4461</v>
+      </c>
+      <c r="K470" t="s">
+        <v>4470</v>
+      </c>
+      <c r="L470" t="s">
+        <v>4471</v>
+      </c>
+      <c r="M470" t="s">
+        <v>4409</v>
+      </c>
+      <c r="N470" t="s">
+        <v>4472</v>
+      </c>
+      <c r="O470" t="s">
+        <v>70</v>
+      </c>
+      <c r="P470" t="s">
+        <v>4473</v>
+      </c>
+      <c r="Q470" t="s">
+        <v>4474</v>
+      </c>
+      <c r="R470" t="s">
+        <v>73</v>
+      </c>
+      <c r="S470" t="s">
+        <v>74</v>
+      </c>
+      <c r="T470" t="s"/>
+      <c r="U470" t="s">
+        <v>75</v>
+      </c>
+      <c r="V470" t="s">
+        <v>4475</v>
+      </c>
+      <c r="W470" t="s"/>
+      <c r="X470" t="s">
+        <v>4476</v>
+      </c>
+      <c r="Y470" t="s"/>
+      <c r="Z470" t="s"/>
+      <c r="AA470" t="s"/>
+      <c r="AB470" t="s"/>
+      <c r="AC470" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="471" spans="1:29">
+      <c r="A471" t="s">
+        <v>4477</v>
+      </c>
+      <c r="B471" t="s">
+        <v>4456</v>
+      </c>
+      <c r="C471" t="s">
+        <v>4457</v>
+      </c>
+      <c r="D471" t="s">
+        <v>4458</v>
+      </c>
+      <c r="E471" t="s">
+        <v>60</v>
+      </c>
+      <c r="F471" t="s">
+        <v>4459</v>
+      </c>
+      <c r="G471" t="s">
+        <v>4460</v>
+      </c>
+      <c r="H471" t="s">
+        <v>195</v>
+      </c>
+      <c r="I471" t="s">
+        <v>196</v>
+      </c>
+      <c r="J471" t="s">
+        <v>4461</v>
+      </c>
+      <c r="K471" t="s">
+        <v>4478</v>
+      </c>
+      <c r="L471" t="s">
+        <v>4479</v>
+      </c>
+      <c r="M471" t="s">
+        <v>4409</v>
+      </c>
+      <c r="N471" t="s">
+        <v>4480</v>
+      </c>
+      <c r="O471" t="s">
+        <v>70</v>
+      </c>
+      <c r="P471" t="s">
+        <v>4481</v>
+      </c>
+      <c r="Q471" t="s">
+        <v>4482</v>
+      </c>
+      <c r="R471" t="s">
+        <v>73</v>
+      </c>
+      <c r="S471" t="s">
+        <v>74</v>
+      </c>
+      <c r="T471" t="s"/>
+      <c r="U471" t="s">
+        <v>75</v>
+      </c>
+      <c r="V471" t="s">
+        <v>4483</v>
+      </c>
+      <c r="W471" t="s"/>
+      <c r="X471" t="s">
+        <v>4484</v>
+      </c>
+      <c r="Y471" t="s"/>
+      <c r="Z471" t="s"/>
+      <c r="AA471" t="s"/>
+      <c r="AB471" t="s"/>
+      <c r="AC471" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="472" spans="1:29">
+      <c r="A472" t="s">
+        <v>4485</v>
+      </c>
+      <c r="B472" t="s">
+        <v>4456</v>
+      </c>
+      <c r="C472" t="s">
+        <v>4457</v>
+      </c>
+      <c r="D472" t="s">
+        <v>4458</v>
+      </c>
+      <c r="E472" t="s">
+        <v>60</v>
+      </c>
+      <c r="F472" t="s">
+        <v>4459</v>
+      </c>
+      <c r="G472" t="s">
+        <v>4460</v>
+      </c>
+      <c r="H472" t="s">
+        <v>195</v>
+      </c>
+      <c r="I472" t="s">
+        <v>196</v>
+      </c>
+      <c r="J472" t="s">
+        <v>4461</v>
+      </c>
+      <c r="K472" t="s">
+        <v>4486</v>
+      </c>
+      <c r="L472" t="s">
+        <v>4487</v>
+      </c>
+      <c r="M472" t="s">
+        <v>4409</v>
+      </c>
+      <c r="N472" t="s">
+        <v>4488</v>
+      </c>
+      <c r="O472" t="s">
+        <v>70</v>
+      </c>
+      <c r="P472" t="s">
+        <v>4489</v>
+      </c>
+      <c r="Q472" t="s">
+        <v>4490</v>
+      </c>
+      <c r="R472" t="s">
+        <v>73</v>
+      </c>
+      <c r="S472" t="s">
+        <v>74</v>
+      </c>
+      <c r="T472" t="s"/>
+      <c r="U472" t="s">
+        <v>75</v>
+      </c>
+      <c r="V472" t="s">
+        <v>4491</v>
+      </c>
+      <c r="W472" t="s"/>
+      <c r="X472" t="s">
+        <v>4492</v>
+      </c>
+      <c r="Y472" t="s"/>
+      <c r="Z472" t="s"/>
+      <c r="AA472" t="s"/>
+      <c r="AB472" t="s"/>
+      <c r="AC472" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="473" spans="1:29">
+      <c r="A473" t="s">
+        <v>4493</v>
+      </c>
+      <c r="B473" t="s">
+        <v>4456</v>
+      </c>
+      <c r="C473" t="s">
+        <v>4457</v>
+      </c>
+      <c r="D473" t="s">
+        <v>4458</v>
+      </c>
+      <c r="E473" t="s">
+        <v>60</v>
+      </c>
+      <c r="F473" t="s">
+        <v>4459</v>
+      </c>
+      <c r="G473" t="s">
+        <v>4460</v>
+      </c>
+      <c r="H473" t="s">
+        <v>195</v>
+      </c>
+      <c r="I473" t="s">
+        <v>196</v>
+      </c>
+      <c r="J473" t="s">
+        <v>4461</v>
+      </c>
+      <c r="K473" t="s">
+        <v>4494</v>
+      </c>
+      <c r="L473" t="s">
+        <v>4495</v>
+      </c>
+      <c r="M473" t="s">
+        <v>4409</v>
+      </c>
+      <c r="N473" t="s">
+        <v>4496</v>
+      </c>
+      <c r="O473" t="s">
+        <v>70</v>
+      </c>
+      <c r="P473" t="s">
+        <v>4497</v>
+      </c>
+      <c r="Q473" t="s">
+        <v>4498</v>
+      </c>
+      <c r="R473" t="s">
+        <v>73</v>
+      </c>
+      <c r="S473" t="s">
+        <v>74</v>
+      </c>
+      <c r="T473" t="s"/>
+      <c r="U473" t="s">
+        <v>75</v>
+      </c>
+      <c r="V473" t="s">
+        <v>4499</v>
+      </c>
+      <c r="W473" t="s"/>
+      <c r="X473" t="s">
+        <v>4500</v>
+      </c>
+      <c r="Y473" t="s"/>
+      <c r="Z473" t="s"/>
+      <c r="AA473" t="s"/>
+      <c r="AB473" t="s"/>
+      <c r="AC473" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="474" spans="1:29">
+      <c r="A474" t="s">
+        <v>4501</v>
+      </c>
+      <c r="B474" t="s">
+        <v>4502</v>
+      </c>
+      <c r="C474" t="s">
+        <v>4503</v>
+      </c>
+      <c r="D474" t="s">
+        <v>4504</v>
+      </c>
+      <c r="E474" t="s">
+        <v>192</v>
+      </c>
+      <c r="F474" t="s">
+        <v>4505</v>
+      </c>
+      <c r="G474" t="s">
+        <v>4506</v>
+      </c>
+      <c r="H474" t="s">
+        <v>195</v>
+      </c>
+      <c r="I474" t="s">
+        <v>196</v>
+      </c>
+      <c r="J474" t="s">
+        <v>4507</v>
+      </c>
+      <c r="K474" t="s">
+        <v>4508</v>
+      </c>
+      <c r="L474" t="s">
+        <v>4509</v>
+      </c>
+      <c r="M474" t="s">
+        <v>4409</v>
+      </c>
+      <c r="N474" t="s">
+        <v>4510</v>
+      </c>
+      <c r="O474" t="s">
+        <v>70</v>
+      </c>
+      <c r="P474" t="s">
+        <v>4511</v>
+      </c>
+      <c r="Q474" t="s">
+        <v>4512</v>
+      </c>
+      <c r="R474" t="s">
+        <v>73</v>
+      </c>
+      <c r="S474" t="s">
+        <v>74</v>
+      </c>
+      <c r="T474" t="s"/>
+      <c r="U474" t="s">
+        <v>75</v>
+      </c>
+      <c r="V474" t="s">
+        <v>4513</v>
+      </c>
+      <c r="W474" t="s"/>
+      <c r="X474" t="s">
+        <v>4514</v>
+      </c>
+      <c r="Y474" t="s"/>
+      <c r="Z474" t="s"/>
+      <c r="AA474" t="s"/>
+      <c r="AB474" t="s"/>
+      <c r="AC474" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="475" spans="1:29">
+      <c r="A475" t="s">
+        <v>4515</v>
+      </c>
+      <c r="B475" t="s">
+        <v>4516</v>
+      </c>
+      <c r="C475" t="s">
+        <v>4517</v>
+      </c>
+      <c r="D475" t="s">
+        <v>4404</v>
+      </c>
+      <c r="E475" t="s">
+        <v>336</v>
+      </c>
+      <c r="F475" t="s">
+        <v>4518</v>
+      </c>
+      <c r="G475" t="s">
+        <v>4519</v>
+      </c>
+      <c r="H475" t="s">
+        <v>195</v>
+      </c>
+      <c r="I475" t="s">
+        <v>196</v>
+      </c>
+      <c r="J475" t="s">
+        <v>4520</v>
+      </c>
+      <c r="K475" t="s">
+        <v>4521</v>
+      </c>
+      <c r="L475" t="s">
+        <v>4522</v>
+      </c>
+      <c r="M475" t="s">
+        <v>4409</v>
+      </c>
+      <c r="N475" t="s">
+        <v>4523</v>
+      </c>
+      <c r="O475" t="s">
+        <v>70</v>
+      </c>
+      <c r="P475" t="s">
+        <v>4524</v>
+      </c>
+      <c r="Q475" t="s">
+        <v>4525</v>
+      </c>
+      <c r="R475" t="s">
+        <v>73</v>
+      </c>
+      <c r="S475" t="s">
+        <v>74</v>
+      </c>
+      <c r="T475" t="s"/>
+      <c r="U475" t="s">
+        <v>75</v>
+      </c>
+      <c r="V475" t="s">
+        <v>4526</v>
+      </c>
+      <c r="W475" t="s"/>
+      <c r="X475" t="s">
+        <v>4527</v>
+      </c>
+      <c r="Y475" t="s"/>
+      <c r="Z475" t="s"/>
+      <c r="AA475" t="s"/>
+      <c r="AB475" t="s"/>
+      <c r="AC475" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="476" spans="1:29">
+      <c r="A476" t="s">
+        <v>4528</v>
+      </c>
+      <c r="B476" t="s">
+        <v>4516</v>
+      </c>
+      <c r="C476" t="s">
+        <v>4517</v>
+      </c>
+      <c r="D476" t="s">
+        <v>4404</v>
+      </c>
+      <c r="E476" t="s">
+        <v>336</v>
+      </c>
+      <c r="F476" t="s">
+        <v>4518</v>
+      </c>
+      <c r="G476" t="s">
+        <v>4519</v>
+      </c>
+      <c r="H476" t="s">
+        <v>195</v>
+      </c>
+      <c r="I476" t="s">
+        <v>196</v>
+      </c>
+      <c r="J476" t="s">
+        <v>4520</v>
+      </c>
+      <c r="K476" t="s">
+        <v>4529</v>
+      </c>
+      <c r="L476" t="s">
+        <v>4530</v>
+      </c>
+      <c r="M476" t="s">
+        <v>4409</v>
+      </c>
+      <c r="N476" t="s">
+        <v>4531</v>
+      </c>
+      <c r="O476" t="s">
+        <v>70</v>
+      </c>
+      <c r="P476" t="s">
+        <v>4532</v>
+      </c>
+      <c r="Q476" t="s">
+        <v>4533</v>
+      </c>
+      <c r="R476" t="s">
+        <v>73</v>
+      </c>
+      <c r="S476" t="s">
+        <v>74</v>
+      </c>
+      <c r="T476" t="s"/>
+      <c r="U476" t="s">
+        <v>75</v>
+      </c>
+      <c r="V476" t="s">
+        <v>4534</v>
+      </c>
+      <c r="W476" t="s"/>
+      <c r="X476" t="s">
+        <v>4535</v>
+      </c>
+      <c r="Y476" t="s"/>
+      <c r="Z476" t="s"/>
+      <c r="AA476" t="s"/>
+      <c r="AB476" t="s"/>
+      <c r="AC476" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="477" spans="1:29">
+      <c r="A477" t="s">
+        <v>4515</v>
+      </c>
+      <c r="B477" t="s">
+        <v>4536</v>
+      </c>
+      <c r="C477" t="s">
+        <v>4517</v>
+      </c>
+      <c r="D477" t="s">
+        <v>4404</v>
+      </c>
+      <c r="E477" t="s">
+        <v>336</v>
+      </c>
+      <c r="F477" t="s">
+        <v>4518</v>
+      </c>
+      <c r="G477" t="s">
+        <v>4537</v>
+      </c>
+      <c r="H477" t="s">
+        <v>195</v>
+      </c>
+      <c r="I477" t="s">
+        <v>196</v>
+      </c>
+      <c r="J477" t="s">
+        <v>4538</v>
+      </c>
+      <c r="K477" t="s">
+        <v>4539</v>
+      </c>
+      <c r="L477" t="s">
+        <v>4540</v>
+      </c>
+      <c r="M477" t="s">
+        <v>4409</v>
+      </c>
+      <c r="N477" t="s">
+        <v>4541</v>
+      </c>
+      <c r="O477" t="s">
+        <v>70</v>
+      </c>
+      <c r="P477" t="s">
+        <v>4542</v>
+      </c>
+      <c r="Q477" t="s">
+        <v>4543</v>
+      </c>
+      <c r="R477" t="s">
+        <v>73</v>
+      </c>
+      <c r="S477" t="s">
+        <v>74</v>
+      </c>
+      <c r="T477" t="s"/>
+      <c r="U477" t="s">
+        <v>75</v>
+      </c>
+      <c r="V477" t="s">
+        <v>4544</v>
+      </c>
+      <c r="W477" t="s"/>
+      <c r="X477" t="s">
+        <v>4545</v>
+      </c>
+      <c r="Y477" t="s"/>
+      <c r="Z477" t="s"/>
+      <c r="AA477" t="s"/>
+      <c r="AB477" t="s"/>
+      <c r="AC477" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="478" spans="1:29">
+      <c r="A478" t="s">
+        <v>4528</v>
+      </c>
+      <c r="B478" t="s">
+        <v>4536</v>
+      </c>
+      <c r="C478" t="s">
+        <v>4517</v>
+      </c>
+      <c r="D478" t="s">
+        <v>4404</v>
+      </c>
+      <c r="E478" t="s">
+        <v>336</v>
+      </c>
+      <c r="F478" t="s">
+        <v>4518</v>
+      </c>
+      <c r="G478" t="s">
+        <v>4537</v>
+      </c>
+      <c r="H478" t="s">
+        <v>195</v>
+      </c>
+      <c r="I478" t="s">
+        <v>196</v>
+      </c>
+      <c r="J478" t="s">
+        <v>4538</v>
+      </c>
+      <c r="K478" t="s">
+        <v>4546</v>
+      </c>
+      <c r="L478" t="s">
+        <v>4547</v>
+      </c>
+      <c r="M478" t="s">
+        <v>4409</v>
+      </c>
+      <c r="N478" t="s">
+        <v>4548</v>
+      </c>
+      <c r="O478" t="s">
+        <v>70</v>
+      </c>
+      <c r="P478" t="s">
+        <v>4549</v>
+      </c>
+      <c r="Q478" t="s">
+        <v>4550</v>
+      </c>
+      <c r="R478" t="s">
+        <v>73</v>
+      </c>
+      <c r="S478" t="s">
+        <v>74</v>
+      </c>
+      <c r="T478" t="s"/>
+      <c r="U478" t="s">
+        <v>75</v>
+      </c>
+      <c r="V478" t="s">
+        <v>4551</v>
+      </c>
+      <c r="W478" t="s"/>
+      <c r="X478" t="s">
+        <v>4552</v>
+      </c>
+      <c r="Y478" t="s"/>
+      <c r="Z478" t="s"/>
+      <c r="AA478" t="s"/>
+      <c r="AB478" t="s"/>
+      <c r="AC478" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="479" spans="1:29">
+      <c r="A479" t="s">
+        <v>4515</v>
+      </c>
+      <c r="B479" t="s">
+        <v>4553</v>
+      </c>
+      <c r="C479" t="s">
+        <v>4517</v>
+      </c>
+      <c r="D479" t="s">
+        <v>4404</v>
+      </c>
+      <c r="E479" t="s">
+        <v>336</v>
+      </c>
+      <c r="F479" t="s">
+        <v>4518</v>
+      </c>
+      <c r="G479" t="s">
+        <v>4554</v>
+      </c>
+      <c r="H479" t="s">
+        <v>195</v>
+      </c>
+      <c r="I479" t="s">
+        <v>196</v>
+      </c>
+      <c r="J479" t="s">
+        <v>4555</v>
+      </c>
+      <c r="K479" t="s">
+        <v>4556</v>
+      </c>
+      <c r="L479" t="s">
+        <v>4557</v>
+      </c>
+      <c r="M479" t="s">
+        <v>4409</v>
+      </c>
+      <c r="N479" t="s">
+        <v>4558</v>
+      </c>
+      <c r="O479" t="s">
+        <v>70</v>
+      </c>
+      <c r="P479" t="s">
+        <v>4559</v>
+      </c>
+      <c r="Q479" t="s">
+        <v>4560</v>
+      </c>
+      <c r="R479" t="s">
+        <v>73</v>
+      </c>
+      <c r="S479" t="s">
+        <v>74</v>
+      </c>
+      <c r="T479" t="s"/>
+      <c r="U479" t="s">
+        <v>75</v>
+      </c>
+      <c r="V479" t="s">
+        <v>4561</v>
+      </c>
+      <c r="W479" t="s"/>
+      <c r="X479" t="s">
+        <v>4562</v>
+      </c>
+      <c r="Y479" t="s"/>
+      <c r="Z479" t="s"/>
+      <c r="AA479" t="s"/>
+      <c r="AB479" t="s"/>
+      <c r="AC479" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="480" spans="1:29">
+      <c r="A480" t="s">
+        <v>4528</v>
+      </c>
+      <c r="B480" t="s">
+        <v>4553</v>
+      </c>
+      <c r="C480" t="s">
+        <v>4517</v>
+      </c>
+      <c r="D480" t="s">
+        <v>4404</v>
+      </c>
+      <c r="E480" t="s">
+        <v>336</v>
+      </c>
+      <c r="F480" t="s">
+        <v>4518</v>
+      </c>
+      <c r="G480" t="s">
+        <v>4554</v>
+      </c>
+      <c r="H480" t="s">
+        <v>195</v>
+      </c>
+      <c r="I480" t="s">
+        <v>196</v>
+      </c>
+      <c r="J480" t="s">
+        <v>4555</v>
+      </c>
+      <c r="K480" t="s">
+        <v>4563</v>
+      </c>
+      <c r="L480" t="s">
+        <v>4564</v>
+      </c>
+      <c r="M480" t="s">
+        <v>4409</v>
+      </c>
+      <c r="N480" t="s">
+        <v>4565</v>
+      </c>
+      <c r="O480" t="s">
+        <v>70</v>
+      </c>
+      <c r="P480" t="s">
+        <v>4566</v>
+      </c>
+      <c r="Q480" t="s">
+        <v>4567</v>
+      </c>
+      <c r="R480" t="s">
+        <v>73</v>
+      </c>
+      <c r="S480" t="s">
+        <v>74</v>
+      </c>
+      <c r="T480" t="s"/>
+      <c r="U480" t="s">
+        <v>75</v>
+      </c>
+      <c r="V480" t="s">
+        <v>4568</v>
+      </c>
+      <c r="W480" t="s"/>
+      <c r="X480" t="s">
+        <v>4569</v>
+      </c>
+      <c r="Y480" t="s"/>
+      <c r="Z480" t="s"/>
+      <c r="AA480" t="s"/>
+      <c r="AB480" t="s"/>
+      <c r="AC480" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="481" spans="1:29">
+      <c r="A481" t="s">
+        <v>4570</v>
+      </c>
+      <c r="B481" t="s">
+        <v>4571</v>
+      </c>
+      <c r="C481" t="s">
+        <v>4572</v>
+      </c>
+      <c r="D481" t="s">
+        <v>4573</v>
+      </c>
+      <c r="E481" t="s">
+        <v>192</v>
+      </c>
+      <c r="F481" t="s">
+        <v>4405</v>
+      </c>
+      <c r="G481" t="s">
+        <v>4314</v>
+      </c>
+      <c r="H481" t="s">
+        <v>195</v>
+      </c>
+      <c r="I481" t="s">
+        <v>196</v>
+      </c>
+      <c r="J481" t="s">
+        <v>4574</v>
+      </c>
+      <c r="K481" t="s">
+        <v>4575</v>
+      </c>
+      <c r="L481" t="s">
+        <v>4576</v>
+      </c>
+      <c r="M481" t="s">
+        <v>4409</v>
+      </c>
+      <c r="N481" t="s">
+        <v>4577</v>
+      </c>
+      <c r="O481" t="s">
+        <v>70</v>
+      </c>
+      <c r="P481" t="s">
+        <v>4578</v>
+      </c>
+      <c r="Q481" t="s">
+        <v>4579</v>
+      </c>
+      <c r="R481" t="s">
+        <v>73</v>
+      </c>
+      <c r="S481" t="s">
+        <v>74</v>
+      </c>
+      <c r="T481" t="s"/>
+      <c r="U481" t="s">
+        <v>75</v>
+      </c>
+      <c r="V481" t="s">
+        <v>4580</v>
+      </c>
+      <c r="W481" t="s"/>
+      <c r="X481" t="s">
+        <v>4581</v>
+      </c>
+      <c r="Y481" t="s"/>
+      <c r="Z481" t="s"/>
+      <c r="AA481" t="s"/>
+      <c r="AB481" t="s"/>
+      <c r="AC481" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="482" spans="1:29">
+      <c r="A482" t="s">
+        <v>4582</v>
+      </c>
+      <c r="B482" t="s">
+        <v>4583</v>
+      </c>
+      <c r="C482" t="s">
+        <v>4572</v>
+      </c>
+      <c r="D482" t="s">
+        <v>4584</v>
+      </c>
+      <c r="E482" t="s">
+        <v>336</v>
+      </c>
+      <c r="F482" t="s">
+        <v>4405</v>
+      </c>
+      <c r="G482" t="s">
+        <v>4314</v>
+      </c>
+      <c r="H482" t="s">
+        <v>195</v>
+      </c>
+      <c r="I482" t="s">
+        <v>196</v>
+      </c>
+      <c r="J482" t="s">
+        <v>4585</v>
+      </c>
+      <c r="K482" t="s">
+        <v>4586</v>
+      </c>
+      <c r="L482" t="s">
+        <v>4587</v>
+      </c>
+      <c r="M482" t="s">
+        <v>4409</v>
+      </c>
+      <c r="N482" t="s">
+        <v>4588</v>
+      </c>
+      <c r="O482" t="s">
+        <v>70</v>
+      </c>
+      <c r="P482" t="s">
+        <v>4589</v>
+      </c>
+      <c r="Q482" t="s">
+        <v>4590</v>
+      </c>
+      <c r="R482" t="s">
+        <v>73</v>
+      </c>
+      <c r="S482" t="s">
+        <v>74</v>
+      </c>
+      <c r="T482" t="s"/>
+      <c r="U482" t="s">
+        <v>75</v>
+      </c>
+      <c r="V482" t="s">
+        <v>4591</v>
+      </c>
+      <c r="W482" t="s"/>
+      <c r="X482" t="s">
+        <v>4592</v>
+      </c>
+      <c r="Y482" t="s"/>
+      <c r="Z482" t="s"/>
+      <c r="AA482" t="s"/>
+      <c r="AB482" t="s"/>
+      <c r="AC482" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="483" spans="1:29">
+      <c r="A483" t="s">
+        <v>4593</v>
+      </c>
+      <c r="B483" t="s">
+        <v>4583</v>
+      </c>
+      <c r="C483" t="s">
+        <v>4572</v>
+      </c>
+      <c r="D483" t="s">
+        <v>4584</v>
+      </c>
+      <c r="E483" t="s">
+        <v>336</v>
+      </c>
+      <c r="F483" t="s">
+        <v>4405</v>
+      </c>
+      <c r="G483" t="s">
+        <v>4314</v>
+      </c>
+      <c r="H483" t="s">
+        <v>195</v>
+      </c>
+      <c r="I483" t="s">
+        <v>196</v>
+      </c>
+      <c r="J483" t="s">
+        <v>4585</v>
+      </c>
+      <c r="K483" t="s">
+        <v>4594</v>
+      </c>
+      <c r="L483" t="s">
+        <v>4595</v>
+      </c>
+      <c r="M483" t="s">
+        <v>4409</v>
+      </c>
+      <c r="N483" t="s">
+        <v>4596</v>
+      </c>
+      <c r="O483" t="s">
+        <v>70</v>
+      </c>
+      <c r="P483" t="s">
+        <v>4597</v>
+      </c>
+      <c r="Q483" t="s">
+        <v>4598</v>
+      </c>
+      <c r="R483" t="s">
+        <v>73</v>
+      </c>
+      <c r="S483" t="s">
+        <v>74</v>
+      </c>
+      <c r="T483" t="s"/>
+      <c r="U483" t="s">
+        <v>75</v>
+      </c>
+      <c r="V483" t="s">
+        <v>4599</v>
+      </c>
+      <c r="W483" t="s"/>
+      <c r="X483" t="s">
+        <v>4600</v>
+      </c>
+      <c r="Y483" t="s"/>
+      <c r="Z483" t="s"/>
+      <c r="AA483" t="s"/>
+      <c r="AB483" t="s"/>
+      <c r="AC483" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="484" spans="1:29">
+      <c r="A484" t="s">
+        <v>4601</v>
+      </c>
+      <c r="B484" t="s">
+        <v>4602</v>
+      </c>
+      <c r="C484" t="s">
+        <v>1621</v>
+      </c>
+      <c r="D484" t="s">
+        <v>4404</v>
+      </c>
+      <c r="E484" t="s">
+        <v>209</v>
+      </c>
+      <c r="F484" t="s">
+        <v>4405</v>
+      </c>
+      <c r="G484" t="s">
+        <v>254</v>
+      </c>
+      <c r="H484" t="s">
+        <v>195</v>
+      </c>
+      <c r="I484" t="s">
+        <v>196</v>
+      </c>
+      <c r="J484" t="s">
+        <v>4603</v>
+      </c>
+      <c r="K484" t="s">
+        <v>4604</v>
+      </c>
+      <c r="L484" t="s">
+        <v>4605</v>
+      </c>
+      <c r="M484" t="s">
+        <v>4409</v>
+      </c>
+      <c r="N484" t="s">
+        <v>4606</v>
+      </c>
+      <c r="O484" t="s">
+        <v>70</v>
+      </c>
+      <c r="P484" t="s">
+        <v>4607</v>
+      </c>
+      <c r="Q484" t="s">
+        <v>4608</v>
+      </c>
+      <c r="R484" t="s">
+        <v>73</v>
+      </c>
+      <c r="S484" t="s">
+        <v>74</v>
+      </c>
+      <c r="T484" t="s"/>
+      <c r="U484" t="s">
+        <v>75</v>
+      </c>
+      <c r="V484" t="s">
+        <v>4609</v>
+      </c>
+      <c r="W484" t="s"/>
+      <c r="X484" t="s">
+        <v>4610</v>
+      </c>
+      <c r="Y484" t="s"/>
+      <c r="Z484" t="s"/>
+      <c r="AA484" t="s"/>
+      <c r="AB484" t="s"/>
+      <c r="AC484" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="485" spans="1:29">
+      <c r="A485" t="s">
+        <v>4611</v>
+      </c>
+      <c r="B485" t="s">
+        <v>4602</v>
+      </c>
+      <c r="C485" t="s">
+        <v>1621</v>
+      </c>
+      <c r="D485" t="s">
+        <v>4404</v>
+      </c>
+      <c r="E485" t="s">
+        <v>209</v>
+      </c>
+      <c r="F485" t="s">
+        <v>4405</v>
+      </c>
+      <c r="G485" t="s">
+        <v>254</v>
+      </c>
+      <c r="H485" t="s">
+        <v>195</v>
+      </c>
+      <c r="I485" t="s">
+        <v>196</v>
+      </c>
+      <c r="J485" t="s">
+        <v>4603</v>
+      </c>
+      <c r="K485" t="s">
+        <v>4612</v>
+      </c>
+      <c r="L485" t="s">
+        <v>4613</v>
+      </c>
+      <c r="M485" t="s">
+        <v>4409</v>
+      </c>
+      <c r="N485" t="s">
+        <v>4614</v>
+      </c>
+      <c r="O485" t="s">
+        <v>70</v>
+      </c>
+      <c r="P485" t="s">
+        <v>4615</v>
+      </c>
+      <c r="Q485" t="s">
+        <v>4616</v>
+      </c>
+      <c r="R485" t="s">
+        <v>73</v>
+      </c>
+      <c r="S485" t="s">
+        <v>74</v>
+      </c>
+      <c r="T485" t="s"/>
+      <c r="U485" t="s">
+        <v>75</v>
+      </c>
+      <c r="V485" t="s">
+        <v>4617</v>
+      </c>
+      <c r="W485" t="s"/>
+      <c r="X485" t="s">
+        <v>4618</v>
+      </c>
+      <c r="Y485" t="s"/>
+      <c r="Z485" t="s"/>
+      <c r="AA485" t="s"/>
+      <c r="AB485" t="s"/>
+      <c r="AC485" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="486" spans="1:29">
+      <c r="A486" t="s">
+        <v>4619</v>
+      </c>
+      <c r="B486" t="s">
+        <v>4602</v>
+      </c>
+      <c r="C486" t="s">
+        <v>1621</v>
+      </c>
+      <c r="D486" t="s">
+        <v>4404</v>
+      </c>
+      <c r="E486" t="s">
+        <v>209</v>
+      </c>
+      <c r="F486" t="s">
+        <v>4405</v>
+      </c>
+      <c r="G486" t="s">
+        <v>254</v>
+      </c>
+      <c r="H486" t="s">
+        <v>195</v>
+      </c>
+      <c r="I486" t="s">
+        <v>196</v>
+      </c>
+      <c r="J486" t="s">
+        <v>4603</v>
+      </c>
+      <c r="K486" t="s">
+        <v>4620</v>
+      </c>
+      <c r="L486" t="s">
+        <v>4621</v>
+      </c>
+      <c r="M486" t="s">
+        <v>4409</v>
+      </c>
+      <c r="N486" t="s">
+        <v>4622</v>
+      </c>
+      <c r="O486" t="s">
+        <v>70</v>
+      </c>
+      <c r="P486" t="s">
+        <v>4623</v>
+      </c>
+      <c r="Q486" t="s">
+        <v>4624</v>
+      </c>
+      <c r="R486" t="s">
+        <v>73</v>
+      </c>
+      <c r="S486" t="s">
+        <v>74</v>
+      </c>
+      <c r="T486" t="s"/>
+      <c r="U486" t="s">
+        <v>75</v>
+      </c>
+      <c r="V486" t="s">
+        <v>4625</v>
+      </c>
+      <c r="W486" t="s"/>
+      <c r="X486" t="s">
+        <v>4626</v>
+      </c>
+      <c r="Y486" t="s"/>
+      <c r="Z486" t="s"/>
+      <c r="AA486" t="s"/>
+      <c r="AB486" t="s"/>
+      <c r="AC486" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="487" spans="1:29">
+      <c r="A487" t="s">
+        <v>4627</v>
+      </c>
+      <c r="B487" t="s">
+        <v>4628</v>
+      </c>
+      <c r="C487" t="s">
+        <v>4629</v>
+      </c>
+      <c r="D487" t="s">
+        <v>4630</v>
+      </c>
+      <c r="E487" t="s">
+        <v>192</v>
+      </c>
+      <c r="F487" t="s">
+        <v>4631</v>
+      </c>
+      <c r="G487" t="s">
+        <v>4632</v>
+      </c>
+      <c r="H487" t="s">
+        <v>195</v>
+      </c>
+      <c r="I487" t="s">
+        <v>196</v>
+      </c>
+      <c r="J487" t="s">
+        <v>4633</v>
+      </c>
+      <c r="K487" t="s">
+        <v>4634</v>
+      </c>
+      <c r="L487" t="s">
+        <v>4635</v>
+      </c>
+      <c r="M487" t="s">
+        <v>4409</v>
+      </c>
+      <c r="N487" t="s">
+        <v>4636</v>
+      </c>
+      <c r="O487" t="s">
+        <v>70</v>
+      </c>
+      <c r="P487" t="s">
+        <v>4637</v>
+      </c>
+      <c r="Q487" t="s">
+        <v>4638</v>
+      </c>
+      <c r="R487" t="s">
+        <v>73</v>
+      </c>
+      <c r="S487" t="s">
+        <v>74</v>
+      </c>
+      <c r="T487" t="s"/>
+      <c r="U487" t="s">
+        <v>75</v>
+      </c>
+      <c r="V487" t="s">
+        <v>4639</v>
+      </c>
+      <c r="W487" t="s"/>
+      <c r="X487" t="s">
+        <v>4640</v>
+      </c>
+      <c r="Y487" t="s"/>
+      <c r="Z487" t="s"/>
+      <c r="AA487" t="s"/>
+      <c r="AB487" t="s"/>
+      <c r="AC487" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="488" spans="1:29">
+      <c r="A488" t="s">
+        <v>4641</v>
+      </c>
+      <c r="B488" t="s">
+        <v>4642</v>
+      </c>
+      <c r="C488" t="s">
+        <v>4643</v>
+      </c>
+      <c r="D488" t="s">
+        <v>4404</v>
+      </c>
+      <c r="E488" t="s">
+        <v>253</v>
+      </c>
+      <c r="F488" t="s">
+        <v>4405</v>
+      </c>
+      <c r="G488" t="s">
+        <v>4314</v>
+      </c>
+      <c r="H488" t="s">
+        <v>195</v>
+      </c>
+      <c r="I488" t="s">
+        <v>196</v>
+      </c>
+      <c r="J488" t="s">
+        <v>4644</v>
+      </c>
+      <c r="K488" t="s">
+        <v>4645</v>
+      </c>
+      <c r="L488" t="s">
+        <v>4646</v>
+      </c>
+      <c r="M488" t="s">
+        <v>4409</v>
+      </c>
+      <c r="N488" t="s">
+        <v>4647</v>
+      </c>
+      <c r="O488" t="s">
+        <v>70</v>
+      </c>
+      <c r="P488" t="s">
+        <v>4648</v>
+      </c>
+      <c r="Q488" t="s">
+        <v>4649</v>
+      </c>
+      <c r="R488" t="s">
+        <v>73</v>
+      </c>
+      <c r="S488" t="s">
+        <v>74</v>
+      </c>
+      <c r="T488" t="s"/>
+      <c r="U488" t="s">
+        <v>75</v>
+      </c>
+      <c r="V488" t="s">
+        <v>4650</v>
+      </c>
+      <c r="W488" t="s"/>
+      <c r="X488" t="s">
+        <v>4651</v>
+      </c>
+      <c r="Y488" t="s"/>
+      <c r="Z488" t="s"/>
+      <c r="AA488" t="s"/>
+      <c r="AB488" t="s"/>
+      <c r="AC488" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="489" spans="1:29">
+      <c r="A489" t="s">
+        <v>4652</v>
+      </c>
+      <c r="B489" t="s">
+        <v>4642</v>
+      </c>
+      <c r="C489" t="s">
+        <v>4643</v>
+      </c>
+      <c r="D489" t="s">
+        <v>4404</v>
+      </c>
+      <c r="E489" t="s">
+        <v>253</v>
+      </c>
+      <c r="F489" t="s">
+        <v>4405</v>
+      </c>
+      <c r="G489" t="s">
+        <v>4314</v>
+      </c>
+      <c r="H489" t="s">
+        <v>195</v>
+      </c>
+      <c r="I489" t="s">
+        <v>196</v>
+      </c>
+      <c r="J489" t="s">
+        <v>4653</v>
+      </c>
+      <c r="K489" t="s">
+        <v>4654</v>
+      </c>
+      <c r="L489" t="s">
+        <v>4655</v>
+      </c>
+      <c r="M489" t="s">
+        <v>4409</v>
+      </c>
+      <c r="N489" t="s">
+        <v>4656</v>
+      </c>
+      <c r="O489" t="s">
+        <v>70</v>
+      </c>
+      <c r="P489" t="s">
+        <v>4657</v>
+      </c>
+      <c r="Q489" t="s">
+        <v>4658</v>
+      </c>
+      <c r="R489" t="s">
+        <v>73</v>
+      </c>
+      <c r="S489" t="s">
+        <v>74</v>
+      </c>
+      <c r="T489" t="s"/>
+      <c r="U489" t="s">
+        <v>75</v>
+      </c>
+      <c r="V489" t="s">
+        <v>4659</v>
+      </c>
+      <c r="W489" t="s"/>
+      <c r="X489" t="s">
+        <v>4660</v>
+      </c>
+      <c r="Y489" t="s"/>
+      <c r="Z489" t="s"/>
+      <c r="AA489" t="s"/>
+      <c r="AB489" t="s"/>
+      <c r="AC489" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="490" spans="1:29">
+      <c r="A490" t="s">
+        <v>4661</v>
+      </c>
+      <c r="B490" t="s">
+        <v>4642</v>
+      </c>
+      <c r="C490" t="s">
+        <v>4643</v>
+      </c>
+      <c r="D490" t="s">
+        <v>4404</v>
+      </c>
+      <c r="E490" t="s">
+        <v>253</v>
+      </c>
+      <c r="F490" t="s">
+        <v>4405</v>
+      </c>
+      <c r="G490" t="s">
+        <v>4314</v>
+      </c>
+      <c r="H490" t="s">
+        <v>195</v>
+      </c>
+      <c r="I490" t="s">
+        <v>196</v>
+      </c>
+      <c r="J490" t="s">
+        <v>4662</v>
+      </c>
+      <c r="K490" t="s">
+        <v>4663</v>
+      </c>
+      <c r="L490" t="s">
+        <v>4664</v>
+      </c>
+      <c r="M490" t="s">
+        <v>4409</v>
+      </c>
+      <c r="N490" t="s">
+        <v>4665</v>
+      </c>
+      <c r="O490" t="s">
+        <v>70</v>
+      </c>
+      <c r="P490" t="s">
+        <v>4666</v>
+      </c>
+      <c r="Q490" t="s">
+        <v>4667</v>
+      </c>
+      <c r="R490" t="s">
+        <v>73</v>
+      </c>
+      <c r="S490" t="s">
+        <v>74</v>
+      </c>
+      <c r="T490" t="s"/>
+      <c r="U490" t="s">
+        <v>75</v>
+      </c>
+      <c r="V490" t="s">
+        <v>4668</v>
+      </c>
+      <c r="W490" t="s"/>
+      <c r="X490" t="s">
+        <v>4669</v>
+      </c>
+      <c r="Y490" t="s"/>
+      <c r="Z490" t="s"/>
+      <c r="AA490" t="s"/>
+      <c r="AB490" t="s"/>
+      <c r="AC490" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="491" spans="1:29">
+      <c r="A491" t="s">
+        <v>4670</v>
+      </c>
+      <c r="B491" t="s">
+        <v>4642</v>
+      </c>
+      <c r="C491" t="s">
+        <v>4643</v>
+      </c>
+      <c r="D491" t="s">
+        <v>4404</v>
+      </c>
+      <c r="E491" t="s">
+        <v>253</v>
+      </c>
+      <c r="F491" t="s">
+        <v>4405</v>
+      </c>
+      <c r="G491" t="s">
+        <v>4314</v>
+      </c>
+      <c r="H491" t="s">
+        <v>195</v>
+      </c>
+      <c r="I491" t="s">
+        <v>196</v>
+      </c>
+      <c r="J491" t="s">
+        <v>4671</v>
+      </c>
+      <c r="K491" t="s">
+        <v>4672</v>
+      </c>
+      <c r="L491" t="s">
+        <v>4673</v>
+      </c>
+      <c r="M491" t="s">
+        <v>4409</v>
+      </c>
+      <c r="N491" t="s">
+        <v>4674</v>
+      </c>
+      <c r="O491" t="s">
+        <v>70</v>
+      </c>
+      <c r="P491" t="s">
+        <v>4675</v>
+      </c>
+      <c r="Q491" t="s">
+        <v>4676</v>
+      </c>
+      <c r="R491" t="s">
+        <v>73</v>
+      </c>
+      <c r="S491" t="s">
+        <v>74</v>
+      </c>
+      <c r="T491" t="s"/>
+      <c r="U491" t="s">
+        <v>75</v>
+      </c>
+      <c r="V491" t="s">
+        <v>4677</v>
+      </c>
+      <c r="W491" t="s"/>
+      <c r="X491" t="s">
+        <v>4678</v>
+      </c>
+      <c r="Y491" t="s"/>
+      <c r="Z491" t="s"/>
+      <c r="AA491" t="s"/>
+      <c r="AB491" t="s"/>
+      <c r="AC491" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="492" spans="1:29">
+      <c r="A492" t="s">
+        <v>4679</v>
+      </c>
+      <c r="B492" t="s">
+        <v>4642</v>
+      </c>
+      <c r="C492" t="s">
+        <v>4643</v>
+      </c>
+      <c r="D492" t="s">
+        <v>4404</v>
+      </c>
+      <c r="E492" t="s">
+        <v>253</v>
+      </c>
+      <c r="F492" t="s">
+        <v>4405</v>
+      </c>
+      <c r="G492" t="s">
+        <v>4314</v>
+      </c>
+      <c r="H492" t="s">
+        <v>195</v>
+      </c>
+      <c r="I492" t="s">
+        <v>196</v>
+      </c>
+      <c r="J492" t="s">
+        <v>4680</v>
+      </c>
+      <c r="K492" t="s">
+        <v>4681</v>
+      </c>
+      <c r="L492" t="s">
+        <v>4682</v>
+      </c>
+      <c r="M492" t="s">
+        <v>4409</v>
+      </c>
+      <c r="N492" t="s">
+        <v>4683</v>
+      </c>
+      <c r="O492" t="s">
+        <v>70</v>
+      </c>
+      <c r="P492" t="s">
+        <v>4684</v>
+      </c>
+      <c r="Q492" t="s">
+        <v>4685</v>
+      </c>
+      <c r="R492" t="s">
+        <v>73</v>
+      </c>
+      <c r="S492" t="s">
+        <v>74</v>
+      </c>
+      <c r="T492" t="s"/>
+      <c r="U492" t="s">
+        <v>75</v>
+      </c>
+      <c r="V492" t="s">
+        <v>4686</v>
+      </c>
+      <c r="W492" t="s"/>
+      <c r="X492" t="s">
+        <v>4687</v>
+      </c>
+      <c r="Y492" t="s"/>
+      <c r="Z492" t="s"/>
+      <c r="AA492" t="s"/>
+      <c r="AB492" t="s"/>
+      <c r="AC492" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="493" spans="1:29">
+      <c r="A493" t="s">
+        <v>4688</v>
+      </c>
+      <c r="B493" t="s">
+        <v>4642</v>
+      </c>
+      <c r="C493" t="s">
+        <v>4643</v>
+      </c>
+      <c r="D493" t="s">
+        <v>4404</v>
+      </c>
+      <c r="E493" t="s">
+        <v>253</v>
+      </c>
+      <c r="F493" t="s">
+        <v>4405</v>
+      </c>
+      <c r="G493" t="s">
+        <v>4314</v>
+      </c>
+      <c r="H493" t="s">
+        <v>195</v>
+      </c>
+      <c r="I493" t="s">
+        <v>196</v>
+      </c>
+      <c r="J493" t="s">
+        <v>4689</v>
+      </c>
+      <c r="K493" t="s">
+        <v>4690</v>
+      </c>
+      <c r="L493" t="s">
+        <v>4691</v>
+      </c>
+      <c r="M493" t="s">
+        <v>4409</v>
+      </c>
+      <c r="N493" t="s">
+        <v>4692</v>
+      </c>
+      <c r="O493" t="s">
+        <v>70</v>
+      </c>
+      <c r="P493" t="s">
+        <v>4693</v>
+      </c>
+      <c r="Q493" t="s">
+        <v>4694</v>
+      </c>
+      <c r="R493" t="s">
+        <v>73</v>
+      </c>
+      <c r="S493" t="s">
+        <v>74</v>
+      </c>
+      <c r="T493" t="s"/>
+      <c r="U493" t="s">
+        <v>75</v>
+      </c>
+      <c r="V493" t="s">
+        <v>4695</v>
+      </c>
+      <c r="W493" t="s"/>
+      <c r="X493" t="s">
+        <v>4696</v>
+      </c>
+      <c r="Y493" t="s"/>
+      <c r="Z493" t="s"/>
+      <c r="AA493" t="s"/>
+      <c r="AB493" t="s"/>
+      <c r="AC493" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="494" spans="1:29">
+      <c r="A494" t="s">
+        <v>4697</v>
+      </c>
+      <c r="B494" t="s">
+        <v>4642</v>
+      </c>
+      <c r="C494" t="s">
+        <v>4643</v>
+      </c>
+      <c r="D494" t="s">
+        <v>4404</v>
+      </c>
+      <c r="E494" t="s">
+        <v>253</v>
+      </c>
+      <c r="F494" t="s">
+        <v>4405</v>
+      </c>
+      <c r="G494" t="s">
+        <v>4314</v>
+      </c>
+      <c r="H494" t="s">
+        <v>195</v>
+      </c>
+      <c r="I494" t="s">
+        <v>196</v>
+      </c>
+      <c r="J494" t="s">
+        <v>4698</v>
+      </c>
+      <c r="K494" t="s">
+        <v>4699</v>
+      </c>
+      <c r="L494" t="s">
+        <v>4700</v>
+      </c>
+      <c r="M494" t="s">
+        <v>4409</v>
+      </c>
+      <c r="N494" t="s">
+        <v>4701</v>
+      </c>
+      <c r="O494" t="s">
+        <v>70</v>
+      </c>
+      <c r="P494" t="s">
+        <v>4702</v>
+      </c>
+      <c r="Q494" t="s">
+        <v>4703</v>
+      </c>
+      <c r="R494" t="s">
+        <v>73</v>
+      </c>
+      <c r="S494" t="s">
+        <v>74</v>
+      </c>
+      <c r="T494" t="s"/>
+      <c r="U494" t="s">
+        <v>75</v>
+      </c>
+      <c r="V494" t="s">
+        <v>4704</v>
+      </c>
+      <c r="W494" t="s"/>
+      <c r="X494" t="s">
+        <v>4705</v>
+      </c>
+      <c r="Y494" t="s"/>
+      <c r="Z494" t="s"/>
+      <c r="AA494" t="s"/>
+      <c r="AB494" t="s"/>
+      <c r="AC494" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="495" spans="1:29">
+      <c r="A495" t="s">
+        <v>4706</v>
+      </c>
+      <c r="B495" t="s">
+        <v>4642</v>
+      </c>
+      <c r="C495" t="s">
+        <v>4643</v>
+      </c>
+      <c r="D495" t="s">
+        <v>4404</v>
+      </c>
+      <c r="E495" t="s">
+        <v>253</v>
+      </c>
+      <c r="F495" t="s">
+        <v>4405</v>
+      </c>
+      <c r="G495" t="s">
+        <v>4314</v>
+      </c>
+      <c r="H495" t="s">
+        <v>195</v>
+      </c>
+      <c r="I495" t="s">
+        <v>196</v>
+      </c>
+      <c r="J495" t="s">
+        <v>4707</v>
+      </c>
+      <c r="K495" t="s">
+        <v>4708</v>
+      </c>
+      <c r="L495" t="s">
+        <v>4709</v>
+      </c>
+      <c r="M495" t="s">
+        <v>4409</v>
+      </c>
+      <c r="N495" t="s">
+        <v>4710</v>
+      </c>
+      <c r="O495" t="s">
+        <v>70</v>
+      </c>
+      <c r="P495" t="s">
+        <v>4711</v>
+      </c>
+      <c r="Q495" t="s">
+        <v>4712</v>
+      </c>
+      <c r="R495" t="s">
+        <v>73</v>
+      </c>
+      <c r="S495" t="s">
+        <v>74</v>
+      </c>
+      <c r="T495" t="s"/>
+      <c r="U495" t="s">
+        <v>75</v>
+      </c>
+      <c r="V495" t="s">
+        <v>4713</v>
+      </c>
+      <c r="W495" t="s"/>
+      <c r="X495" t="s">
+        <v>4714</v>
+      </c>
+      <c r="Y495" t="s"/>
+      <c r="Z495" t="s"/>
+      <c r="AA495" t="s"/>
+      <c r="AB495" t="s"/>
+      <c r="AC495" t="n">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
